--- a/Compititor's_Price/Celotex_Prices/Celotex_Prices_28-07-2025.xlsx
+++ b/Compititor's_Price/Celotex_Prices/Celotex_Prices_28-07-2025.xlsx
@@ -591,25 +591,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=138.0.7204.169); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff7bc3ce935+77845]
-	GetHandleVerifier [0x0x7ff7bc3ce990+77936]
-	(No symbol) [0x0x7ff7bc189cda]
-	(No symbol) [0x0x7ff7bc1e06aa]
-	(No symbol) [0x0x7ff7bc1e095c]
-	(No symbol) [0x0x7ff7bc233d07]
-	(No symbol) [0x0x7ff7bc20890f]
-	(No symbol) [0x0x7ff7bc230b07]
-	(No symbol) [0x0x7ff7bc2086a3]
-	(No symbol) [0x0x7ff7bc1d1791]
-	(No symbol) [0x0x7ff7bc1d2523]
-	GetHandleVerifier [0x0x7ff7bc6a684d+3059501]
-	GetHandleVerifier [0x0x7ff7bc6a0c0d+3035885]
-	GetHandleVerifier [0x0x7ff7bc6c0400+3164896]
-	GetHandleVerifier [0x0x7ff7bc3e8c3e+185118]
-	GetHandleVerifier [0x0x7ff7bc3f054f+216111]
-	GetHandleVerifier [0x0x7ff7bc3d72e4+113092]
-	GetHandleVerifier [0x0x7ff7bc3d7499+113529]
-	GetHandleVerifier [0x0x7ff7bc3be298+10616]
+	GetHandleVerifier [0x0x7ff6ece1e935+77845]
+	GetHandleVerifier [0x0x7ff6ece1e990+77936]
+	(No symbol) [0x0x7ff6ecbd9cda]
+	(No symbol) [0x0x7ff6ecc306aa]
+	(No symbol) [0x0x7ff6ecc3095c]
+	(No symbol) [0x0x7ff6ecc83d07]
+	(No symbol) [0x0x7ff6ecc5890f]
+	(No symbol) [0x0x7ff6ecc80b07]
+	(No symbol) [0x0x7ff6ecc586a3]
+	(No symbol) [0x0x7ff6ecc21791]
+	(No symbol) [0x0x7ff6ecc22523]
+	GetHandleVerifier [0x0x7ff6ed0f684d+3059501]
+	GetHandleVerifier [0x0x7ff6ed0f0c0d+3035885]
+	GetHandleVerifier [0x0x7ff6ed110400+3164896]
+	GetHandleVerifier [0x0x7ff6ece38c3e+185118]
+	GetHandleVerifier [0x0x7ff6ece4054f+216111]
+	GetHandleVerifier [0x0x7ff6ece272e4+113092]
+	GetHandleVerifier [0x0x7ff6ece27499+113529]
+	GetHandleVerifier [0x0x7ff6ece0e298+10616]
 	BaseThreadInitThunk [0x0x7ffb1377e8d7+23]
 	RtlUserThreadStart [0x0x7ffb157fc34c+44]
 </t>
@@ -712,25 +712,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=138.0.7204.169); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff7bc3ce935+77845]
-	GetHandleVerifier [0x0x7ff7bc3ce990+77936]
-	(No symbol) [0x0x7ff7bc189cda]
-	(No symbol) [0x0x7ff7bc1e06aa]
-	(No symbol) [0x0x7ff7bc1e095c]
-	(No symbol) [0x0x7ff7bc233d07]
-	(No symbol) [0x0x7ff7bc20890f]
-	(No symbol) [0x0x7ff7bc230b07]
-	(No symbol) [0x0x7ff7bc2086a3]
-	(No symbol) [0x0x7ff7bc1d1791]
-	(No symbol) [0x0x7ff7bc1d2523]
-	GetHandleVerifier [0x0x7ff7bc6a684d+3059501]
-	GetHandleVerifier [0x0x7ff7bc6a0c0d+3035885]
-	GetHandleVerifier [0x0x7ff7bc6c0400+3164896]
-	GetHandleVerifier [0x0x7ff7bc3e8c3e+185118]
-	GetHandleVerifier [0x0x7ff7bc3f054f+216111]
-	GetHandleVerifier [0x0x7ff7bc3d72e4+113092]
-	GetHandleVerifier [0x0x7ff7bc3d7499+113529]
-	GetHandleVerifier [0x0x7ff7bc3be298+10616]
+	GetHandleVerifier [0x0x7ff6ece1e935+77845]
+	GetHandleVerifier [0x0x7ff6ece1e990+77936]
+	(No symbol) [0x0x7ff6ecbd9cda]
+	(No symbol) [0x0x7ff6ecc306aa]
+	(No symbol) [0x0x7ff6ecc3095c]
+	(No symbol) [0x0x7ff6ecc83d07]
+	(No symbol) [0x0x7ff6ecc5890f]
+	(No symbol) [0x0x7ff6ecc80b07]
+	(No symbol) [0x0x7ff6ecc586a3]
+	(No symbol) [0x0x7ff6ecc21791]
+	(No symbol) [0x0x7ff6ecc22523]
+	GetHandleVerifier [0x0x7ff6ed0f684d+3059501]
+	GetHandleVerifier [0x0x7ff6ed0f0c0d+3035885]
+	GetHandleVerifier [0x0x7ff6ed110400+3164896]
+	GetHandleVerifier [0x0x7ff6ece38c3e+185118]
+	GetHandleVerifier [0x0x7ff6ece4054f+216111]
+	GetHandleVerifier [0x0x7ff6ece272e4+113092]
+	GetHandleVerifier [0x0x7ff6ece27499+113529]
+	GetHandleVerifier [0x0x7ff6ece0e298+10616]
 	BaseThreadInitThunk [0x0x7ffb1377e8d7+23]
 	RtlUserThreadStart [0x0x7ffb157fc34c+44]
 </t>
@@ -833,25 +833,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=138.0.7204.169); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff7bc3ce935+77845]
-	GetHandleVerifier [0x0x7ff7bc3ce990+77936]
-	(No symbol) [0x0x7ff7bc189cda]
-	(No symbol) [0x0x7ff7bc1e06aa]
-	(No symbol) [0x0x7ff7bc1e095c]
-	(No symbol) [0x0x7ff7bc233d07]
-	(No symbol) [0x0x7ff7bc20890f]
-	(No symbol) [0x0x7ff7bc230b07]
-	(No symbol) [0x0x7ff7bc2086a3]
-	(No symbol) [0x0x7ff7bc1d1791]
-	(No symbol) [0x0x7ff7bc1d2523]
-	GetHandleVerifier [0x0x7ff7bc6a684d+3059501]
-	GetHandleVerifier [0x0x7ff7bc6a0c0d+3035885]
-	GetHandleVerifier [0x0x7ff7bc6c0400+3164896]
-	GetHandleVerifier [0x0x7ff7bc3e8c3e+185118]
-	GetHandleVerifier [0x0x7ff7bc3f054f+216111]
-	GetHandleVerifier [0x0x7ff7bc3d72e4+113092]
-	GetHandleVerifier [0x0x7ff7bc3d7499+113529]
-	GetHandleVerifier [0x0x7ff7bc3be298+10616]
+	GetHandleVerifier [0x0x7ff6ece1e935+77845]
+	GetHandleVerifier [0x0x7ff6ece1e990+77936]
+	(No symbol) [0x0x7ff6ecbd9cda]
+	(No symbol) [0x0x7ff6ecc306aa]
+	(No symbol) [0x0x7ff6ecc3095c]
+	(No symbol) [0x0x7ff6ecc83d07]
+	(No symbol) [0x0x7ff6ecc5890f]
+	(No symbol) [0x0x7ff6ecc80b07]
+	(No symbol) [0x0x7ff6ecc586a3]
+	(No symbol) [0x0x7ff6ecc21791]
+	(No symbol) [0x0x7ff6ecc22523]
+	GetHandleVerifier [0x0x7ff6ed0f684d+3059501]
+	GetHandleVerifier [0x0x7ff6ed0f0c0d+3035885]
+	GetHandleVerifier [0x0x7ff6ed110400+3164896]
+	GetHandleVerifier [0x0x7ff6ece38c3e+185118]
+	GetHandleVerifier [0x0x7ff6ece4054f+216111]
+	GetHandleVerifier [0x0x7ff6ece272e4+113092]
+	GetHandleVerifier [0x0x7ff6ece27499+113529]
+	GetHandleVerifier [0x0x7ff6ece0e298+10616]
 	BaseThreadInitThunk [0x0x7ffb1377e8d7+23]
 	RtlUserThreadStart [0x0x7ffb157fc34c+44]
 </t>
@@ -954,25 +954,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=138.0.7204.169); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff7bc3ce935+77845]
-	GetHandleVerifier [0x0x7ff7bc3ce990+77936]
-	(No symbol) [0x0x7ff7bc189cda]
-	(No symbol) [0x0x7ff7bc1e06aa]
-	(No symbol) [0x0x7ff7bc1e095c]
-	(No symbol) [0x0x7ff7bc233d07]
-	(No symbol) [0x0x7ff7bc20890f]
-	(No symbol) [0x0x7ff7bc230b07]
-	(No symbol) [0x0x7ff7bc2086a3]
-	(No symbol) [0x0x7ff7bc1d1791]
-	(No symbol) [0x0x7ff7bc1d2523]
-	GetHandleVerifier [0x0x7ff7bc6a684d+3059501]
-	GetHandleVerifier [0x0x7ff7bc6a0c0d+3035885]
-	GetHandleVerifier [0x0x7ff7bc6c0400+3164896]
-	GetHandleVerifier [0x0x7ff7bc3e8c3e+185118]
-	GetHandleVerifier [0x0x7ff7bc3f054f+216111]
-	GetHandleVerifier [0x0x7ff7bc3d72e4+113092]
-	GetHandleVerifier [0x0x7ff7bc3d7499+113529]
-	GetHandleVerifier [0x0x7ff7bc3be298+10616]
+	GetHandleVerifier [0x0x7ff6ece1e935+77845]
+	GetHandleVerifier [0x0x7ff6ece1e990+77936]
+	(No symbol) [0x0x7ff6ecbd9cda]
+	(No symbol) [0x0x7ff6ecc306aa]
+	(No symbol) [0x0x7ff6ecc3095c]
+	(No symbol) [0x0x7ff6ecc83d07]
+	(No symbol) [0x0x7ff6ecc5890f]
+	(No symbol) [0x0x7ff6ecc80b07]
+	(No symbol) [0x0x7ff6ecc586a3]
+	(No symbol) [0x0x7ff6ecc21791]
+	(No symbol) [0x0x7ff6ecc22523]
+	GetHandleVerifier [0x0x7ff6ed0f684d+3059501]
+	GetHandleVerifier [0x0x7ff6ed0f0c0d+3035885]
+	GetHandleVerifier [0x0x7ff6ed110400+3164896]
+	GetHandleVerifier [0x0x7ff6ece38c3e+185118]
+	GetHandleVerifier [0x0x7ff6ece4054f+216111]
+	GetHandleVerifier [0x0x7ff6ece272e4+113092]
+	GetHandleVerifier [0x0x7ff6ece27499+113529]
+	GetHandleVerifier [0x0x7ff6ece0e298+10616]
 	BaseThreadInitThunk [0x0x7ffb1377e8d7+23]
 	RtlUserThreadStart [0x0x7ffb157fc34c+44]
 </t>
@@ -1075,25 +1075,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=138.0.7204.169); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff7bc3ce935+77845]
-	GetHandleVerifier [0x0x7ff7bc3ce990+77936]
-	(No symbol) [0x0x7ff7bc189cda]
-	(No symbol) [0x0x7ff7bc1e06aa]
-	(No symbol) [0x0x7ff7bc1e095c]
-	(No symbol) [0x0x7ff7bc233d07]
-	(No symbol) [0x0x7ff7bc20890f]
-	(No symbol) [0x0x7ff7bc230b07]
-	(No symbol) [0x0x7ff7bc2086a3]
-	(No symbol) [0x0x7ff7bc1d1791]
-	(No symbol) [0x0x7ff7bc1d2523]
-	GetHandleVerifier [0x0x7ff7bc6a684d+3059501]
-	GetHandleVerifier [0x0x7ff7bc6a0c0d+3035885]
-	GetHandleVerifier [0x0x7ff7bc6c0400+3164896]
-	GetHandleVerifier [0x0x7ff7bc3e8c3e+185118]
-	GetHandleVerifier [0x0x7ff7bc3f054f+216111]
-	GetHandleVerifier [0x0x7ff7bc3d72e4+113092]
-	GetHandleVerifier [0x0x7ff7bc3d7499+113529]
-	GetHandleVerifier [0x0x7ff7bc3be298+10616]
+	GetHandleVerifier [0x0x7ff6ece1e935+77845]
+	GetHandleVerifier [0x0x7ff6ece1e990+77936]
+	(No symbol) [0x0x7ff6ecbd9cda]
+	(No symbol) [0x0x7ff6ecc306aa]
+	(No symbol) [0x0x7ff6ecc3095c]
+	(No symbol) [0x0x7ff6ecc83d07]
+	(No symbol) [0x0x7ff6ecc5890f]
+	(No symbol) [0x0x7ff6ecc80b07]
+	(No symbol) [0x0x7ff6ecc586a3]
+	(No symbol) [0x0x7ff6ecc21791]
+	(No symbol) [0x0x7ff6ecc22523]
+	GetHandleVerifier [0x0x7ff6ed0f684d+3059501]
+	GetHandleVerifier [0x0x7ff6ed0f0c0d+3035885]
+	GetHandleVerifier [0x0x7ff6ed110400+3164896]
+	GetHandleVerifier [0x0x7ff6ece38c3e+185118]
+	GetHandleVerifier [0x0x7ff6ece4054f+216111]
+	GetHandleVerifier [0x0x7ff6ece272e4+113092]
+	GetHandleVerifier [0x0x7ff6ece27499+113529]
+	GetHandleVerifier [0x0x7ff6ece0e298+10616]
 	BaseThreadInitThunk [0x0x7ffb1377e8d7+23]
 	RtlUserThreadStart [0x0x7ffb157fc34c+44]
 </t>
@@ -1196,25 +1196,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=138.0.7204.169); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff7bc3ce935+77845]
-	GetHandleVerifier [0x0x7ff7bc3ce990+77936]
-	(No symbol) [0x0x7ff7bc189cda]
-	(No symbol) [0x0x7ff7bc1e06aa]
-	(No symbol) [0x0x7ff7bc1e095c]
-	(No symbol) [0x0x7ff7bc233d07]
-	(No symbol) [0x0x7ff7bc20890f]
-	(No symbol) [0x0x7ff7bc230b07]
-	(No symbol) [0x0x7ff7bc2086a3]
-	(No symbol) [0x0x7ff7bc1d1791]
-	(No symbol) [0x0x7ff7bc1d2523]
-	GetHandleVerifier [0x0x7ff7bc6a684d+3059501]
-	GetHandleVerifier [0x0x7ff7bc6a0c0d+3035885]
-	GetHandleVerifier [0x0x7ff7bc6c0400+3164896]
-	GetHandleVerifier [0x0x7ff7bc3e8c3e+185118]
-	GetHandleVerifier [0x0x7ff7bc3f054f+216111]
-	GetHandleVerifier [0x0x7ff7bc3d72e4+113092]
-	GetHandleVerifier [0x0x7ff7bc3d7499+113529]
-	GetHandleVerifier [0x0x7ff7bc3be298+10616]
+	GetHandleVerifier [0x0x7ff6ece1e935+77845]
+	GetHandleVerifier [0x0x7ff6ece1e990+77936]
+	(No symbol) [0x0x7ff6ecbd9cda]
+	(No symbol) [0x0x7ff6ecc306aa]
+	(No symbol) [0x0x7ff6ecc3095c]
+	(No symbol) [0x0x7ff6ecc83d07]
+	(No symbol) [0x0x7ff6ecc5890f]
+	(No symbol) [0x0x7ff6ecc80b07]
+	(No symbol) [0x0x7ff6ecc586a3]
+	(No symbol) [0x0x7ff6ecc21791]
+	(No symbol) [0x0x7ff6ecc22523]
+	GetHandleVerifier [0x0x7ff6ed0f684d+3059501]
+	GetHandleVerifier [0x0x7ff6ed0f0c0d+3035885]
+	GetHandleVerifier [0x0x7ff6ed110400+3164896]
+	GetHandleVerifier [0x0x7ff6ece38c3e+185118]
+	GetHandleVerifier [0x0x7ff6ece4054f+216111]
+	GetHandleVerifier [0x0x7ff6ece272e4+113092]
+	GetHandleVerifier [0x0x7ff6ece27499+113529]
+	GetHandleVerifier [0x0x7ff6ece0e298+10616]
 	BaseThreadInitThunk [0x0x7ffb1377e8d7+23]
 	RtlUserThreadStart [0x0x7ffb157fc34c+44]
 </t>
@@ -1317,25 +1317,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=138.0.7204.169); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff7bc3ce935+77845]
-	GetHandleVerifier [0x0x7ff7bc3ce990+77936]
-	(No symbol) [0x0x7ff7bc189cda]
-	(No symbol) [0x0x7ff7bc1e06aa]
-	(No symbol) [0x0x7ff7bc1e095c]
-	(No symbol) [0x0x7ff7bc233d07]
-	(No symbol) [0x0x7ff7bc20890f]
-	(No symbol) [0x0x7ff7bc230b07]
-	(No symbol) [0x0x7ff7bc2086a3]
-	(No symbol) [0x0x7ff7bc1d1791]
-	(No symbol) [0x0x7ff7bc1d2523]
-	GetHandleVerifier [0x0x7ff7bc6a684d+3059501]
-	GetHandleVerifier [0x0x7ff7bc6a0c0d+3035885]
-	GetHandleVerifier [0x0x7ff7bc6c0400+3164896]
-	GetHandleVerifier [0x0x7ff7bc3e8c3e+185118]
-	GetHandleVerifier [0x0x7ff7bc3f054f+216111]
-	GetHandleVerifier [0x0x7ff7bc3d72e4+113092]
-	GetHandleVerifier [0x0x7ff7bc3d7499+113529]
-	GetHandleVerifier [0x0x7ff7bc3be298+10616]
+	GetHandleVerifier [0x0x7ff6ece1e935+77845]
+	GetHandleVerifier [0x0x7ff6ece1e990+77936]
+	(No symbol) [0x0x7ff6ecbd9cda]
+	(No symbol) [0x0x7ff6ecc306aa]
+	(No symbol) [0x0x7ff6ecc3095c]
+	(No symbol) [0x0x7ff6ecc83d07]
+	(No symbol) [0x0x7ff6ecc5890f]
+	(No symbol) [0x0x7ff6ecc80b07]
+	(No symbol) [0x0x7ff6ecc586a3]
+	(No symbol) [0x0x7ff6ecc21791]
+	(No symbol) [0x0x7ff6ecc22523]
+	GetHandleVerifier [0x0x7ff6ed0f684d+3059501]
+	GetHandleVerifier [0x0x7ff6ed0f0c0d+3035885]
+	GetHandleVerifier [0x0x7ff6ed110400+3164896]
+	GetHandleVerifier [0x0x7ff6ece38c3e+185118]
+	GetHandleVerifier [0x0x7ff6ece4054f+216111]
+	GetHandleVerifier [0x0x7ff6ece272e4+113092]
+	GetHandleVerifier [0x0x7ff6ece27499+113529]
+	GetHandleVerifier [0x0x7ff6ece0e298+10616]
 	BaseThreadInitThunk [0x0x7ffb1377e8d7+23]
 	RtlUserThreadStart [0x0x7ffb157fc34c+44]
 </t>
@@ -1438,25 +1438,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=138.0.7204.169); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff7bc3ce935+77845]
-	GetHandleVerifier [0x0x7ff7bc3ce990+77936]
-	(No symbol) [0x0x7ff7bc189cda]
-	(No symbol) [0x0x7ff7bc1e06aa]
-	(No symbol) [0x0x7ff7bc1e095c]
-	(No symbol) [0x0x7ff7bc233d07]
-	(No symbol) [0x0x7ff7bc20890f]
-	(No symbol) [0x0x7ff7bc230b07]
-	(No symbol) [0x0x7ff7bc2086a3]
-	(No symbol) [0x0x7ff7bc1d1791]
-	(No symbol) [0x0x7ff7bc1d2523]
-	GetHandleVerifier [0x0x7ff7bc6a684d+3059501]
-	GetHandleVerifier [0x0x7ff7bc6a0c0d+3035885]
-	GetHandleVerifier [0x0x7ff7bc6c0400+3164896]
-	GetHandleVerifier [0x0x7ff7bc3e8c3e+185118]
-	GetHandleVerifier [0x0x7ff7bc3f054f+216111]
-	GetHandleVerifier [0x0x7ff7bc3d72e4+113092]
-	GetHandleVerifier [0x0x7ff7bc3d7499+113529]
-	GetHandleVerifier [0x0x7ff7bc3be298+10616]
+	GetHandleVerifier [0x0x7ff6ece1e935+77845]
+	GetHandleVerifier [0x0x7ff6ece1e990+77936]
+	(No symbol) [0x0x7ff6ecbd9cda]
+	(No symbol) [0x0x7ff6ecc306aa]
+	(No symbol) [0x0x7ff6ecc3095c]
+	(No symbol) [0x0x7ff6ecc83d07]
+	(No symbol) [0x0x7ff6ecc5890f]
+	(No symbol) [0x0x7ff6ecc80b07]
+	(No symbol) [0x0x7ff6ecc586a3]
+	(No symbol) [0x0x7ff6ecc21791]
+	(No symbol) [0x0x7ff6ecc22523]
+	GetHandleVerifier [0x0x7ff6ed0f684d+3059501]
+	GetHandleVerifier [0x0x7ff6ed0f0c0d+3035885]
+	GetHandleVerifier [0x0x7ff6ed110400+3164896]
+	GetHandleVerifier [0x0x7ff6ece38c3e+185118]
+	GetHandleVerifier [0x0x7ff6ece4054f+216111]
+	GetHandleVerifier [0x0x7ff6ece272e4+113092]
+	GetHandleVerifier [0x0x7ff6ece27499+113529]
+	GetHandleVerifier [0x0x7ff6ece0e298+10616]
 	BaseThreadInitThunk [0x0x7ffb1377e8d7+23]
 	RtlUserThreadStart [0x0x7ffb157fc34c+44]
 </t>
@@ -1559,25 +1559,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=138.0.7204.169); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff7bc3ce935+77845]
-	GetHandleVerifier [0x0x7ff7bc3ce990+77936]
-	(No symbol) [0x0x7ff7bc189cda]
-	(No symbol) [0x0x7ff7bc1e06aa]
-	(No symbol) [0x0x7ff7bc1e095c]
-	(No symbol) [0x0x7ff7bc233d07]
-	(No symbol) [0x0x7ff7bc20890f]
-	(No symbol) [0x0x7ff7bc230b07]
-	(No symbol) [0x0x7ff7bc2086a3]
-	(No symbol) [0x0x7ff7bc1d1791]
-	(No symbol) [0x0x7ff7bc1d2523]
-	GetHandleVerifier [0x0x7ff7bc6a684d+3059501]
-	GetHandleVerifier [0x0x7ff7bc6a0c0d+3035885]
-	GetHandleVerifier [0x0x7ff7bc6c0400+3164896]
-	GetHandleVerifier [0x0x7ff7bc3e8c3e+185118]
-	GetHandleVerifier [0x0x7ff7bc3f054f+216111]
-	GetHandleVerifier [0x0x7ff7bc3d72e4+113092]
-	GetHandleVerifier [0x0x7ff7bc3d7499+113529]
-	GetHandleVerifier [0x0x7ff7bc3be298+10616]
+	GetHandleVerifier [0x0x7ff6ece1e935+77845]
+	GetHandleVerifier [0x0x7ff6ece1e990+77936]
+	(No symbol) [0x0x7ff6ecbd9cda]
+	(No symbol) [0x0x7ff6ecc306aa]
+	(No symbol) [0x0x7ff6ecc3095c]
+	(No symbol) [0x0x7ff6ecc83d07]
+	(No symbol) [0x0x7ff6ecc5890f]
+	(No symbol) [0x0x7ff6ecc80b07]
+	(No symbol) [0x0x7ff6ecc586a3]
+	(No symbol) [0x0x7ff6ecc21791]
+	(No symbol) [0x0x7ff6ecc22523]
+	GetHandleVerifier [0x0x7ff6ed0f684d+3059501]
+	GetHandleVerifier [0x0x7ff6ed0f0c0d+3035885]
+	GetHandleVerifier [0x0x7ff6ed110400+3164896]
+	GetHandleVerifier [0x0x7ff6ece38c3e+185118]
+	GetHandleVerifier [0x0x7ff6ece4054f+216111]
+	GetHandleVerifier [0x0x7ff6ece272e4+113092]
+	GetHandleVerifier [0x0x7ff6ece27499+113529]
+	GetHandleVerifier [0x0x7ff6ece0e298+10616]
 	BaseThreadInitThunk [0x0x7ffb1377e8d7+23]
 	RtlUserThreadStart [0x0x7ffb157fc34c+44]
 </t>
@@ -1680,25 +1680,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=138.0.7204.169); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff7bc3ce935+77845]
-	GetHandleVerifier [0x0x7ff7bc3ce990+77936]
-	(No symbol) [0x0x7ff7bc189cda]
-	(No symbol) [0x0x7ff7bc1e06aa]
-	(No symbol) [0x0x7ff7bc1e095c]
-	(No symbol) [0x0x7ff7bc233d07]
-	(No symbol) [0x0x7ff7bc20890f]
-	(No symbol) [0x0x7ff7bc230b07]
-	(No symbol) [0x0x7ff7bc2086a3]
-	(No symbol) [0x0x7ff7bc1d1791]
-	(No symbol) [0x0x7ff7bc1d2523]
-	GetHandleVerifier [0x0x7ff7bc6a684d+3059501]
-	GetHandleVerifier [0x0x7ff7bc6a0c0d+3035885]
-	GetHandleVerifier [0x0x7ff7bc6c0400+3164896]
-	GetHandleVerifier [0x0x7ff7bc3e8c3e+185118]
-	GetHandleVerifier [0x0x7ff7bc3f054f+216111]
-	GetHandleVerifier [0x0x7ff7bc3d72e4+113092]
-	GetHandleVerifier [0x0x7ff7bc3d7499+113529]
-	GetHandleVerifier [0x0x7ff7bc3be298+10616]
+	GetHandleVerifier [0x0x7ff6ece1e935+77845]
+	GetHandleVerifier [0x0x7ff6ece1e990+77936]
+	(No symbol) [0x0x7ff6ecbd9cda]
+	(No symbol) [0x0x7ff6ecc306aa]
+	(No symbol) [0x0x7ff6ecc3095c]
+	(No symbol) [0x0x7ff6ecc83d07]
+	(No symbol) [0x0x7ff6ecc5890f]
+	(No symbol) [0x0x7ff6ecc80b07]
+	(No symbol) [0x0x7ff6ecc586a3]
+	(No symbol) [0x0x7ff6ecc21791]
+	(No symbol) [0x0x7ff6ecc22523]
+	GetHandleVerifier [0x0x7ff6ed0f684d+3059501]
+	GetHandleVerifier [0x0x7ff6ed0f0c0d+3035885]
+	GetHandleVerifier [0x0x7ff6ed110400+3164896]
+	GetHandleVerifier [0x0x7ff6ece38c3e+185118]
+	GetHandleVerifier [0x0x7ff6ece4054f+216111]
+	GetHandleVerifier [0x0x7ff6ece272e4+113092]
+	GetHandleVerifier [0x0x7ff6ece27499+113529]
+	GetHandleVerifier [0x0x7ff6ece0e298+10616]
 	BaseThreadInitThunk [0x0x7ffb1377e8d7+23]
 	RtlUserThreadStart [0x0x7ffb157fc34c+44]
 </t>
@@ -1801,25 +1801,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=138.0.7204.169); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff7bc3ce935+77845]
-	GetHandleVerifier [0x0x7ff7bc3ce990+77936]
-	(No symbol) [0x0x7ff7bc189cda]
-	(No symbol) [0x0x7ff7bc1e06aa]
-	(No symbol) [0x0x7ff7bc1e095c]
-	(No symbol) [0x0x7ff7bc233d07]
-	(No symbol) [0x0x7ff7bc20890f]
-	(No symbol) [0x0x7ff7bc230b07]
-	(No symbol) [0x0x7ff7bc2086a3]
-	(No symbol) [0x0x7ff7bc1d1791]
-	(No symbol) [0x0x7ff7bc1d2523]
-	GetHandleVerifier [0x0x7ff7bc6a684d+3059501]
-	GetHandleVerifier [0x0x7ff7bc6a0c0d+3035885]
-	GetHandleVerifier [0x0x7ff7bc6c0400+3164896]
-	GetHandleVerifier [0x0x7ff7bc3e8c3e+185118]
-	GetHandleVerifier [0x0x7ff7bc3f054f+216111]
-	GetHandleVerifier [0x0x7ff7bc3d72e4+113092]
-	GetHandleVerifier [0x0x7ff7bc3d7499+113529]
-	GetHandleVerifier [0x0x7ff7bc3be298+10616]
+	GetHandleVerifier [0x0x7ff6ece1e935+77845]
+	GetHandleVerifier [0x0x7ff6ece1e990+77936]
+	(No symbol) [0x0x7ff6ecbd9cda]
+	(No symbol) [0x0x7ff6ecc306aa]
+	(No symbol) [0x0x7ff6ecc3095c]
+	(No symbol) [0x0x7ff6ecc83d07]
+	(No symbol) [0x0x7ff6ecc5890f]
+	(No symbol) [0x0x7ff6ecc80b07]
+	(No symbol) [0x0x7ff6ecc586a3]
+	(No symbol) [0x0x7ff6ecc21791]
+	(No symbol) [0x0x7ff6ecc22523]
+	GetHandleVerifier [0x0x7ff6ed0f684d+3059501]
+	GetHandleVerifier [0x0x7ff6ed0f0c0d+3035885]
+	GetHandleVerifier [0x0x7ff6ed110400+3164896]
+	GetHandleVerifier [0x0x7ff6ece38c3e+185118]
+	GetHandleVerifier [0x0x7ff6ece4054f+216111]
+	GetHandleVerifier [0x0x7ff6ece272e4+113092]
+	GetHandleVerifier [0x0x7ff6ece27499+113529]
+	GetHandleVerifier [0x0x7ff6ece0e298+10616]
 	BaseThreadInitThunk [0x0x7ffb1377e8d7+23]
 	RtlUserThreadStart [0x0x7ffb157fc34c+44]
 </t>
@@ -1922,25 +1922,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=138.0.7204.169); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff7bc3ce935+77845]
-	GetHandleVerifier [0x0x7ff7bc3ce990+77936]
-	(No symbol) [0x0x7ff7bc189cda]
-	(No symbol) [0x0x7ff7bc1e06aa]
-	(No symbol) [0x0x7ff7bc1e095c]
-	(No symbol) [0x0x7ff7bc233d07]
-	(No symbol) [0x0x7ff7bc20890f]
-	(No symbol) [0x0x7ff7bc230b07]
-	(No symbol) [0x0x7ff7bc2086a3]
-	(No symbol) [0x0x7ff7bc1d1791]
-	(No symbol) [0x0x7ff7bc1d2523]
-	GetHandleVerifier [0x0x7ff7bc6a684d+3059501]
-	GetHandleVerifier [0x0x7ff7bc6a0c0d+3035885]
-	GetHandleVerifier [0x0x7ff7bc6c0400+3164896]
-	GetHandleVerifier [0x0x7ff7bc3e8c3e+185118]
-	GetHandleVerifier [0x0x7ff7bc3f054f+216111]
-	GetHandleVerifier [0x0x7ff7bc3d72e4+113092]
-	GetHandleVerifier [0x0x7ff7bc3d7499+113529]
-	GetHandleVerifier [0x0x7ff7bc3be298+10616]
+	GetHandleVerifier [0x0x7ff6ece1e935+77845]
+	GetHandleVerifier [0x0x7ff6ece1e990+77936]
+	(No symbol) [0x0x7ff6ecbd9cda]
+	(No symbol) [0x0x7ff6ecc306aa]
+	(No symbol) [0x0x7ff6ecc3095c]
+	(No symbol) [0x0x7ff6ecc83d07]
+	(No symbol) [0x0x7ff6ecc5890f]
+	(No symbol) [0x0x7ff6ecc80b07]
+	(No symbol) [0x0x7ff6ecc586a3]
+	(No symbol) [0x0x7ff6ecc21791]
+	(No symbol) [0x0x7ff6ecc22523]
+	GetHandleVerifier [0x0x7ff6ed0f684d+3059501]
+	GetHandleVerifier [0x0x7ff6ed0f0c0d+3035885]
+	GetHandleVerifier [0x0x7ff6ed110400+3164896]
+	GetHandleVerifier [0x0x7ff6ece38c3e+185118]
+	GetHandleVerifier [0x0x7ff6ece4054f+216111]
+	GetHandleVerifier [0x0x7ff6ece272e4+113092]
+	GetHandleVerifier [0x0x7ff6ece27499+113529]
+	GetHandleVerifier [0x0x7ff6ece0e298+10616]
 	BaseThreadInitThunk [0x0x7ffb1377e8d7+23]
 	RtlUserThreadStart [0x0x7ffb157fc34c+44]
 </t>
@@ -2043,25 +2043,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=138.0.7204.169); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff7bc3ce935+77845]
-	GetHandleVerifier [0x0x7ff7bc3ce990+77936]
-	(No symbol) [0x0x7ff7bc189cda]
-	(No symbol) [0x0x7ff7bc1e06aa]
-	(No symbol) [0x0x7ff7bc1e095c]
-	(No symbol) [0x0x7ff7bc233d07]
-	(No symbol) [0x0x7ff7bc20890f]
-	(No symbol) [0x0x7ff7bc230b07]
-	(No symbol) [0x0x7ff7bc2086a3]
-	(No symbol) [0x0x7ff7bc1d1791]
-	(No symbol) [0x0x7ff7bc1d2523]
-	GetHandleVerifier [0x0x7ff7bc6a684d+3059501]
-	GetHandleVerifier [0x0x7ff7bc6a0c0d+3035885]
-	GetHandleVerifier [0x0x7ff7bc6c0400+3164896]
-	GetHandleVerifier [0x0x7ff7bc3e8c3e+185118]
-	GetHandleVerifier [0x0x7ff7bc3f054f+216111]
-	GetHandleVerifier [0x0x7ff7bc3d72e4+113092]
-	GetHandleVerifier [0x0x7ff7bc3d7499+113529]
-	GetHandleVerifier [0x0x7ff7bc3be298+10616]
+	GetHandleVerifier [0x0x7ff6ece1e935+77845]
+	GetHandleVerifier [0x0x7ff6ece1e990+77936]
+	(No symbol) [0x0x7ff6ecbd9cda]
+	(No symbol) [0x0x7ff6ecc306aa]
+	(No symbol) [0x0x7ff6ecc3095c]
+	(No symbol) [0x0x7ff6ecc83d07]
+	(No symbol) [0x0x7ff6ecc5890f]
+	(No symbol) [0x0x7ff6ecc80b07]
+	(No symbol) [0x0x7ff6ecc586a3]
+	(No symbol) [0x0x7ff6ecc21791]
+	(No symbol) [0x0x7ff6ecc22523]
+	GetHandleVerifier [0x0x7ff6ed0f684d+3059501]
+	GetHandleVerifier [0x0x7ff6ed0f0c0d+3035885]
+	GetHandleVerifier [0x0x7ff6ed110400+3164896]
+	GetHandleVerifier [0x0x7ff6ece38c3e+185118]
+	GetHandleVerifier [0x0x7ff6ece4054f+216111]
+	GetHandleVerifier [0x0x7ff6ece272e4+113092]
+	GetHandleVerifier [0x0x7ff6ece27499+113529]
+	GetHandleVerifier [0x0x7ff6ece0e298+10616]
 	BaseThreadInitThunk [0x0x7ffb1377e8d7+23]
 	RtlUserThreadStart [0x0x7ffb157fc34c+44]
 </t>
@@ -2164,25 +2164,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=138.0.7204.169); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff7bc3ce935+77845]
-	GetHandleVerifier [0x0x7ff7bc3ce990+77936]
-	(No symbol) [0x0x7ff7bc189cda]
-	(No symbol) [0x0x7ff7bc1e06aa]
-	(No symbol) [0x0x7ff7bc1e095c]
-	(No symbol) [0x0x7ff7bc233d07]
-	(No symbol) [0x0x7ff7bc20890f]
-	(No symbol) [0x0x7ff7bc230b07]
-	(No symbol) [0x0x7ff7bc2086a3]
-	(No symbol) [0x0x7ff7bc1d1791]
-	(No symbol) [0x0x7ff7bc1d2523]
-	GetHandleVerifier [0x0x7ff7bc6a684d+3059501]
-	GetHandleVerifier [0x0x7ff7bc6a0c0d+3035885]
-	GetHandleVerifier [0x0x7ff7bc6c0400+3164896]
-	GetHandleVerifier [0x0x7ff7bc3e8c3e+185118]
-	GetHandleVerifier [0x0x7ff7bc3f054f+216111]
-	GetHandleVerifier [0x0x7ff7bc3d72e4+113092]
-	GetHandleVerifier [0x0x7ff7bc3d7499+113529]
-	GetHandleVerifier [0x0x7ff7bc3be298+10616]
+	GetHandleVerifier [0x0x7ff6ece1e935+77845]
+	GetHandleVerifier [0x0x7ff6ece1e990+77936]
+	(No symbol) [0x0x7ff6ecbd9cda]
+	(No symbol) [0x0x7ff6ecc306aa]
+	(No symbol) [0x0x7ff6ecc3095c]
+	(No symbol) [0x0x7ff6ecc83d07]
+	(No symbol) [0x0x7ff6ecc5890f]
+	(No symbol) [0x0x7ff6ecc80b07]
+	(No symbol) [0x0x7ff6ecc586a3]
+	(No symbol) [0x0x7ff6ecc21791]
+	(No symbol) [0x0x7ff6ecc22523]
+	GetHandleVerifier [0x0x7ff6ed0f684d+3059501]
+	GetHandleVerifier [0x0x7ff6ed0f0c0d+3035885]
+	GetHandleVerifier [0x0x7ff6ed110400+3164896]
+	GetHandleVerifier [0x0x7ff6ece38c3e+185118]
+	GetHandleVerifier [0x0x7ff6ece4054f+216111]
+	GetHandleVerifier [0x0x7ff6ece272e4+113092]
+	GetHandleVerifier [0x0x7ff6ece27499+113529]
+	GetHandleVerifier [0x0x7ff6ece0e298+10616]
 	BaseThreadInitThunk [0x0x7ffb1377e8d7+23]
 	RtlUserThreadStart [0x0x7ffb157fc34c+44]
 </t>
@@ -2285,25 +2285,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=138.0.7204.169); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff7bc3ce935+77845]
-	GetHandleVerifier [0x0x7ff7bc3ce990+77936]
-	(No symbol) [0x0x7ff7bc189cda]
-	(No symbol) [0x0x7ff7bc1e06aa]
-	(No symbol) [0x0x7ff7bc1e095c]
-	(No symbol) [0x0x7ff7bc233d07]
-	(No symbol) [0x0x7ff7bc20890f]
-	(No symbol) [0x0x7ff7bc230b07]
-	(No symbol) [0x0x7ff7bc2086a3]
-	(No symbol) [0x0x7ff7bc1d1791]
-	(No symbol) [0x0x7ff7bc1d2523]
-	GetHandleVerifier [0x0x7ff7bc6a684d+3059501]
-	GetHandleVerifier [0x0x7ff7bc6a0c0d+3035885]
-	GetHandleVerifier [0x0x7ff7bc6c0400+3164896]
-	GetHandleVerifier [0x0x7ff7bc3e8c3e+185118]
-	GetHandleVerifier [0x0x7ff7bc3f054f+216111]
-	GetHandleVerifier [0x0x7ff7bc3d72e4+113092]
-	GetHandleVerifier [0x0x7ff7bc3d7499+113529]
-	GetHandleVerifier [0x0x7ff7bc3be298+10616]
+	GetHandleVerifier [0x0x7ff6ece1e935+77845]
+	GetHandleVerifier [0x0x7ff6ece1e990+77936]
+	(No symbol) [0x0x7ff6ecbd9cda]
+	(No symbol) [0x0x7ff6ecc306aa]
+	(No symbol) [0x0x7ff6ecc3095c]
+	(No symbol) [0x0x7ff6ecc83d07]
+	(No symbol) [0x0x7ff6ecc5890f]
+	(No symbol) [0x0x7ff6ecc80b07]
+	(No symbol) [0x0x7ff6ecc586a3]
+	(No symbol) [0x0x7ff6ecc21791]
+	(No symbol) [0x0x7ff6ecc22523]
+	GetHandleVerifier [0x0x7ff6ed0f684d+3059501]
+	GetHandleVerifier [0x0x7ff6ed0f0c0d+3035885]
+	GetHandleVerifier [0x0x7ff6ed110400+3164896]
+	GetHandleVerifier [0x0x7ff6ece38c3e+185118]
+	GetHandleVerifier [0x0x7ff6ece4054f+216111]
+	GetHandleVerifier [0x0x7ff6ece272e4+113092]
+	GetHandleVerifier [0x0x7ff6ece27499+113529]
+	GetHandleVerifier [0x0x7ff6ece0e298+10616]
 	BaseThreadInitThunk [0x0x7ffb1377e8d7+23]
 	RtlUserThreadStart [0x0x7ffb157fc34c+44]
 </t>
@@ -2503,25 +2503,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=138.0.7204.169); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff7bc3ce935+77845]
-	GetHandleVerifier [0x0x7ff7bc3ce990+77936]
-	(No symbol) [0x0x7ff7bc189cda]
-	(No symbol) [0x0x7ff7bc1e06aa]
-	(No symbol) [0x0x7ff7bc1e095c]
-	(No symbol) [0x0x7ff7bc233d07]
-	(No symbol) [0x0x7ff7bc20890f]
-	(No symbol) [0x0x7ff7bc230b07]
-	(No symbol) [0x0x7ff7bc2086a3]
-	(No symbol) [0x0x7ff7bc1d1791]
-	(No symbol) [0x0x7ff7bc1d2523]
-	GetHandleVerifier [0x0x7ff7bc6a684d+3059501]
-	GetHandleVerifier [0x0x7ff7bc6a0c0d+3035885]
-	GetHandleVerifier [0x0x7ff7bc6c0400+3164896]
-	GetHandleVerifier [0x0x7ff7bc3e8c3e+185118]
-	GetHandleVerifier [0x0x7ff7bc3f054f+216111]
-	GetHandleVerifier [0x0x7ff7bc3d72e4+113092]
-	GetHandleVerifier [0x0x7ff7bc3d7499+113529]
-	GetHandleVerifier [0x0x7ff7bc3be298+10616]
+	GetHandleVerifier [0x0x7ff6ece1e935+77845]
+	GetHandleVerifier [0x0x7ff6ece1e990+77936]
+	(No symbol) [0x0x7ff6ecbd9cda]
+	(No symbol) [0x0x7ff6ecc306aa]
+	(No symbol) [0x0x7ff6ecc3095c]
+	(No symbol) [0x0x7ff6ecc83d07]
+	(No symbol) [0x0x7ff6ecc5890f]
+	(No symbol) [0x0x7ff6ecc80b07]
+	(No symbol) [0x0x7ff6ecc586a3]
+	(No symbol) [0x0x7ff6ecc21791]
+	(No symbol) [0x0x7ff6ecc22523]
+	GetHandleVerifier [0x0x7ff6ed0f684d+3059501]
+	GetHandleVerifier [0x0x7ff6ed0f0c0d+3035885]
+	GetHandleVerifier [0x0x7ff6ed110400+3164896]
+	GetHandleVerifier [0x0x7ff6ece38c3e+185118]
+	GetHandleVerifier [0x0x7ff6ece4054f+216111]
+	GetHandleVerifier [0x0x7ff6ece272e4+113092]
+	GetHandleVerifier [0x0x7ff6ece27499+113529]
+	GetHandleVerifier [0x0x7ff6ece0e298+10616]
 	BaseThreadInitThunk [0x0x7ffb1377e8d7+23]
 	RtlUserThreadStart [0x0x7ffb157fc34c+44]
 </t>
@@ -2624,25 +2624,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=138.0.7204.169); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff7bc3ce935+77845]
-	GetHandleVerifier [0x0x7ff7bc3ce990+77936]
-	(No symbol) [0x0x7ff7bc189cda]
-	(No symbol) [0x0x7ff7bc1e06aa]
-	(No symbol) [0x0x7ff7bc1e095c]
-	(No symbol) [0x0x7ff7bc233d07]
-	(No symbol) [0x0x7ff7bc20890f]
-	(No symbol) [0x0x7ff7bc230b07]
-	(No symbol) [0x0x7ff7bc2086a3]
-	(No symbol) [0x0x7ff7bc1d1791]
-	(No symbol) [0x0x7ff7bc1d2523]
-	GetHandleVerifier [0x0x7ff7bc6a684d+3059501]
-	GetHandleVerifier [0x0x7ff7bc6a0c0d+3035885]
-	GetHandleVerifier [0x0x7ff7bc6c0400+3164896]
-	GetHandleVerifier [0x0x7ff7bc3e8c3e+185118]
-	GetHandleVerifier [0x0x7ff7bc3f054f+216111]
-	GetHandleVerifier [0x0x7ff7bc3d72e4+113092]
-	GetHandleVerifier [0x0x7ff7bc3d7499+113529]
-	GetHandleVerifier [0x0x7ff7bc3be298+10616]
+	GetHandleVerifier [0x0x7ff6ece1e935+77845]
+	GetHandleVerifier [0x0x7ff6ece1e990+77936]
+	(No symbol) [0x0x7ff6ecbd9cda]
+	(No symbol) [0x0x7ff6ecc306aa]
+	(No symbol) [0x0x7ff6ecc3095c]
+	(No symbol) [0x0x7ff6ecc83d07]
+	(No symbol) [0x0x7ff6ecc5890f]
+	(No symbol) [0x0x7ff6ecc80b07]
+	(No symbol) [0x0x7ff6ecc586a3]
+	(No symbol) [0x0x7ff6ecc21791]
+	(No symbol) [0x0x7ff6ecc22523]
+	GetHandleVerifier [0x0x7ff6ed0f684d+3059501]
+	GetHandleVerifier [0x0x7ff6ed0f0c0d+3035885]
+	GetHandleVerifier [0x0x7ff6ed110400+3164896]
+	GetHandleVerifier [0x0x7ff6ece38c3e+185118]
+	GetHandleVerifier [0x0x7ff6ece4054f+216111]
+	GetHandleVerifier [0x0x7ff6ece272e4+113092]
+	GetHandleVerifier [0x0x7ff6ece27499+113529]
+	GetHandleVerifier [0x0x7ff6ece0e298+10616]
 	BaseThreadInitThunk [0x0x7ffb1377e8d7+23]
 	RtlUserThreadStart [0x0x7ffb157fc34c+44]
 </t>
@@ -2745,25 +2745,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=138.0.7204.169); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff7bc3ce935+77845]
-	GetHandleVerifier [0x0x7ff7bc3ce990+77936]
-	(No symbol) [0x0x7ff7bc189cda]
-	(No symbol) [0x0x7ff7bc1e06aa]
-	(No symbol) [0x0x7ff7bc1e095c]
-	(No symbol) [0x0x7ff7bc233d07]
-	(No symbol) [0x0x7ff7bc20890f]
-	(No symbol) [0x0x7ff7bc230b07]
-	(No symbol) [0x0x7ff7bc2086a3]
-	(No symbol) [0x0x7ff7bc1d1791]
-	(No symbol) [0x0x7ff7bc1d2523]
-	GetHandleVerifier [0x0x7ff7bc6a684d+3059501]
-	GetHandleVerifier [0x0x7ff7bc6a0c0d+3035885]
-	GetHandleVerifier [0x0x7ff7bc6c0400+3164896]
-	GetHandleVerifier [0x0x7ff7bc3e8c3e+185118]
-	GetHandleVerifier [0x0x7ff7bc3f054f+216111]
-	GetHandleVerifier [0x0x7ff7bc3d72e4+113092]
-	GetHandleVerifier [0x0x7ff7bc3d7499+113529]
-	GetHandleVerifier [0x0x7ff7bc3be298+10616]
+	GetHandleVerifier [0x0x7ff6ece1e935+77845]
+	GetHandleVerifier [0x0x7ff6ece1e990+77936]
+	(No symbol) [0x0x7ff6ecbd9cda]
+	(No symbol) [0x0x7ff6ecc306aa]
+	(No symbol) [0x0x7ff6ecc3095c]
+	(No symbol) [0x0x7ff6ecc83d07]
+	(No symbol) [0x0x7ff6ecc5890f]
+	(No symbol) [0x0x7ff6ecc80b07]
+	(No symbol) [0x0x7ff6ecc586a3]
+	(No symbol) [0x0x7ff6ecc21791]
+	(No symbol) [0x0x7ff6ecc22523]
+	GetHandleVerifier [0x0x7ff6ed0f684d+3059501]
+	GetHandleVerifier [0x0x7ff6ed0f0c0d+3035885]
+	GetHandleVerifier [0x0x7ff6ed110400+3164896]
+	GetHandleVerifier [0x0x7ff6ece38c3e+185118]
+	GetHandleVerifier [0x0x7ff6ece4054f+216111]
+	GetHandleVerifier [0x0x7ff6ece272e4+113092]
+	GetHandleVerifier [0x0x7ff6ece27499+113529]
+	GetHandleVerifier [0x0x7ff6ece0e298+10616]
 	BaseThreadInitThunk [0x0x7ffb1377e8d7+23]
 	RtlUserThreadStart [0x0x7ffb157fc34c+44]
 </t>
@@ -2866,25 +2866,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=138.0.7204.169); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff7bc3ce935+77845]
-	GetHandleVerifier [0x0x7ff7bc3ce990+77936]
-	(No symbol) [0x0x7ff7bc189cda]
-	(No symbol) [0x0x7ff7bc1e06aa]
-	(No symbol) [0x0x7ff7bc1e095c]
-	(No symbol) [0x0x7ff7bc233d07]
-	(No symbol) [0x0x7ff7bc20890f]
-	(No symbol) [0x0x7ff7bc230b07]
-	(No symbol) [0x0x7ff7bc2086a3]
-	(No symbol) [0x0x7ff7bc1d1791]
-	(No symbol) [0x0x7ff7bc1d2523]
-	GetHandleVerifier [0x0x7ff7bc6a684d+3059501]
-	GetHandleVerifier [0x0x7ff7bc6a0c0d+3035885]
-	GetHandleVerifier [0x0x7ff7bc6c0400+3164896]
-	GetHandleVerifier [0x0x7ff7bc3e8c3e+185118]
-	GetHandleVerifier [0x0x7ff7bc3f054f+216111]
-	GetHandleVerifier [0x0x7ff7bc3d72e4+113092]
-	GetHandleVerifier [0x0x7ff7bc3d7499+113529]
-	GetHandleVerifier [0x0x7ff7bc3be298+10616]
+	GetHandleVerifier [0x0x7ff6ece1e935+77845]
+	GetHandleVerifier [0x0x7ff6ece1e990+77936]
+	(No symbol) [0x0x7ff6ecbd9cda]
+	(No symbol) [0x0x7ff6ecc306aa]
+	(No symbol) [0x0x7ff6ecc3095c]
+	(No symbol) [0x0x7ff6ecc83d07]
+	(No symbol) [0x0x7ff6ecc5890f]
+	(No symbol) [0x0x7ff6ecc80b07]
+	(No symbol) [0x0x7ff6ecc586a3]
+	(No symbol) [0x0x7ff6ecc21791]
+	(No symbol) [0x0x7ff6ecc22523]
+	GetHandleVerifier [0x0x7ff6ed0f684d+3059501]
+	GetHandleVerifier [0x0x7ff6ed0f0c0d+3035885]
+	GetHandleVerifier [0x0x7ff6ed110400+3164896]
+	GetHandleVerifier [0x0x7ff6ece38c3e+185118]
+	GetHandleVerifier [0x0x7ff6ece4054f+216111]
+	GetHandleVerifier [0x0x7ff6ece272e4+113092]
+	GetHandleVerifier [0x0x7ff6ece27499+113529]
+	GetHandleVerifier [0x0x7ff6ece0e298+10616]
 	BaseThreadInitThunk [0x0x7ffb1377e8d7+23]
 	RtlUserThreadStart [0x0x7ffb157fc34c+44]
 </t>
@@ -2987,25 +2987,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=138.0.7204.169); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff7bc3ce935+77845]
-	GetHandleVerifier [0x0x7ff7bc3ce990+77936]
-	(No symbol) [0x0x7ff7bc189cda]
-	(No symbol) [0x0x7ff7bc1e06aa]
-	(No symbol) [0x0x7ff7bc1e095c]
-	(No symbol) [0x0x7ff7bc233d07]
-	(No symbol) [0x0x7ff7bc20890f]
-	(No symbol) [0x0x7ff7bc230b07]
-	(No symbol) [0x0x7ff7bc2086a3]
-	(No symbol) [0x0x7ff7bc1d1791]
-	(No symbol) [0x0x7ff7bc1d2523]
-	GetHandleVerifier [0x0x7ff7bc6a684d+3059501]
-	GetHandleVerifier [0x0x7ff7bc6a0c0d+3035885]
-	GetHandleVerifier [0x0x7ff7bc6c0400+3164896]
-	GetHandleVerifier [0x0x7ff7bc3e8c3e+185118]
-	GetHandleVerifier [0x0x7ff7bc3f054f+216111]
-	GetHandleVerifier [0x0x7ff7bc3d72e4+113092]
-	GetHandleVerifier [0x0x7ff7bc3d7499+113529]
-	GetHandleVerifier [0x0x7ff7bc3be298+10616]
+	GetHandleVerifier [0x0x7ff6ece1e935+77845]
+	GetHandleVerifier [0x0x7ff6ece1e990+77936]
+	(No symbol) [0x0x7ff6ecbd9cda]
+	(No symbol) [0x0x7ff6ecc306aa]
+	(No symbol) [0x0x7ff6ecc3095c]
+	(No symbol) [0x0x7ff6ecc83d07]
+	(No symbol) [0x0x7ff6ecc5890f]
+	(No symbol) [0x0x7ff6ecc80b07]
+	(No symbol) [0x0x7ff6ecc586a3]
+	(No symbol) [0x0x7ff6ecc21791]
+	(No symbol) [0x0x7ff6ecc22523]
+	GetHandleVerifier [0x0x7ff6ed0f684d+3059501]
+	GetHandleVerifier [0x0x7ff6ed0f0c0d+3035885]
+	GetHandleVerifier [0x0x7ff6ed110400+3164896]
+	GetHandleVerifier [0x0x7ff6ece38c3e+185118]
+	GetHandleVerifier [0x0x7ff6ece4054f+216111]
+	GetHandleVerifier [0x0x7ff6ece272e4+113092]
+	GetHandleVerifier [0x0x7ff6ece27499+113529]
+	GetHandleVerifier [0x0x7ff6ece0e298+10616]
 	BaseThreadInitThunk [0x0x7ffb1377e8d7+23]
 	RtlUserThreadStart [0x0x7ffb157fc34c+44]
 </t>
@@ -3108,25 +3108,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=138.0.7204.169); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff7bc3ce935+77845]
-	GetHandleVerifier [0x0x7ff7bc3ce990+77936]
-	(No symbol) [0x0x7ff7bc189cda]
-	(No symbol) [0x0x7ff7bc1e06aa]
-	(No symbol) [0x0x7ff7bc1e095c]
-	(No symbol) [0x0x7ff7bc233d07]
-	(No symbol) [0x0x7ff7bc20890f]
-	(No symbol) [0x0x7ff7bc230b07]
-	(No symbol) [0x0x7ff7bc2086a3]
-	(No symbol) [0x0x7ff7bc1d1791]
-	(No symbol) [0x0x7ff7bc1d2523]
-	GetHandleVerifier [0x0x7ff7bc6a684d+3059501]
-	GetHandleVerifier [0x0x7ff7bc6a0c0d+3035885]
-	GetHandleVerifier [0x0x7ff7bc6c0400+3164896]
-	GetHandleVerifier [0x0x7ff7bc3e8c3e+185118]
-	GetHandleVerifier [0x0x7ff7bc3f054f+216111]
-	GetHandleVerifier [0x0x7ff7bc3d72e4+113092]
-	GetHandleVerifier [0x0x7ff7bc3d7499+113529]
-	GetHandleVerifier [0x0x7ff7bc3be298+10616]
+	GetHandleVerifier [0x0x7ff6ece1e935+77845]
+	GetHandleVerifier [0x0x7ff6ece1e990+77936]
+	(No symbol) [0x0x7ff6ecbd9cda]
+	(No symbol) [0x0x7ff6ecc306aa]
+	(No symbol) [0x0x7ff6ecc3095c]
+	(No symbol) [0x0x7ff6ecc83d07]
+	(No symbol) [0x0x7ff6ecc5890f]
+	(No symbol) [0x0x7ff6ecc80b07]
+	(No symbol) [0x0x7ff6ecc586a3]
+	(No symbol) [0x0x7ff6ecc21791]
+	(No symbol) [0x0x7ff6ecc22523]
+	GetHandleVerifier [0x0x7ff6ed0f684d+3059501]
+	GetHandleVerifier [0x0x7ff6ed0f0c0d+3035885]
+	GetHandleVerifier [0x0x7ff6ed110400+3164896]
+	GetHandleVerifier [0x0x7ff6ece38c3e+185118]
+	GetHandleVerifier [0x0x7ff6ece4054f+216111]
+	GetHandleVerifier [0x0x7ff6ece272e4+113092]
+	GetHandleVerifier [0x0x7ff6ece27499+113529]
+	GetHandleVerifier [0x0x7ff6ece0e298+10616]
 	BaseThreadInitThunk [0x0x7ffb1377e8d7+23]
 	RtlUserThreadStart [0x0x7ffb157fc34c+44]
 </t>
@@ -3229,25 +3229,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=138.0.7204.169); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff7bc3ce935+77845]
-	GetHandleVerifier [0x0x7ff7bc3ce990+77936]
-	(No symbol) [0x0x7ff7bc189cda]
-	(No symbol) [0x0x7ff7bc1e06aa]
-	(No symbol) [0x0x7ff7bc1e095c]
-	(No symbol) [0x0x7ff7bc233d07]
-	(No symbol) [0x0x7ff7bc20890f]
-	(No symbol) [0x0x7ff7bc230b07]
-	(No symbol) [0x0x7ff7bc2086a3]
-	(No symbol) [0x0x7ff7bc1d1791]
-	(No symbol) [0x0x7ff7bc1d2523]
-	GetHandleVerifier [0x0x7ff7bc6a684d+3059501]
-	GetHandleVerifier [0x0x7ff7bc6a0c0d+3035885]
-	GetHandleVerifier [0x0x7ff7bc6c0400+3164896]
-	GetHandleVerifier [0x0x7ff7bc3e8c3e+185118]
-	GetHandleVerifier [0x0x7ff7bc3f054f+216111]
-	GetHandleVerifier [0x0x7ff7bc3d72e4+113092]
-	GetHandleVerifier [0x0x7ff7bc3d7499+113529]
-	GetHandleVerifier [0x0x7ff7bc3be298+10616]
+	GetHandleVerifier [0x0x7ff6ece1e935+77845]
+	GetHandleVerifier [0x0x7ff6ece1e990+77936]
+	(No symbol) [0x0x7ff6ecbd9cda]
+	(No symbol) [0x0x7ff6ecc306aa]
+	(No symbol) [0x0x7ff6ecc3095c]
+	(No symbol) [0x0x7ff6ecc83d07]
+	(No symbol) [0x0x7ff6ecc5890f]
+	(No symbol) [0x0x7ff6ecc80b07]
+	(No symbol) [0x0x7ff6ecc586a3]
+	(No symbol) [0x0x7ff6ecc21791]
+	(No symbol) [0x0x7ff6ecc22523]
+	GetHandleVerifier [0x0x7ff6ed0f684d+3059501]
+	GetHandleVerifier [0x0x7ff6ed0f0c0d+3035885]
+	GetHandleVerifier [0x0x7ff6ed110400+3164896]
+	GetHandleVerifier [0x0x7ff6ece38c3e+185118]
+	GetHandleVerifier [0x0x7ff6ece4054f+216111]
+	GetHandleVerifier [0x0x7ff6ece272e4+113092]
+	GetHandleVerifier [0x0x7ff6ece27499+113529]
+	GetHandleVerifier [0x0x7ff6ece0e298+10616]
 	BaseThreadInitThunk [0x0x7ffb1377e8d7+23]
 	RtlUserThreadStart [0x0x7ffb157fc34c+44]
 </t>
@@ -3350,25 +3350,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=138.0.7204.169); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff7bc3ce935+77845]
-	GetHandleVerifier [0x0x7ff7bc3ce990+77936]
-	(No symbol) [0x0x7ff7bc189cda]
-	(No symbol) [0x0x7ff7bc1e06aa]
-	(No symbol) [0x0x7ff7bc1e095c]
-	(No symbol) [0x0x7ff7bc233d07]
-	(No symbol) [0x0x7ff7bc20890f]
-	(No symbol) [0x0x7ff7bc230b07]
-	(No symbol) [0x0x7ff7bc2086a3]
-	(No symbol) [0x0x7ff7bc1d1791]
-	(No symbol) [0x0x7ff7bc1d2523]
-	GetHandleVerifier [0x0x7ff7bc6a684d+3059501]
-	GetHandleVerifier [0x0x7ff7bc6a0c0d+3035885]
-	GetHandleVerifier [0x0x7ff7bc6c0400+3164896]
-	GetHandleVerifier [0x0x7ff7bc3e8c3e+185118]
-	GetHandleVerifier [0x0x7ff7bc3f054f+216111]
-	GetHandleVerifier [0x0x7ff7bc3d72e4+113092]
-	GetHandleVerifier [0x0x7ff7bc3d7499+113529]
-	GetHandleVerifier [0x0x7ff7bc3be298+10616]
+	GetHandleVerifier [0x0x7ff6ece1e935+77845]
+	GetHandleVerifier [0x0x7ff6ece1e990+77936]
+	(No symbol) [0x0x7ff6ecbd9cda]
+	(No symbol) [0x0x7ff6ecc306aa]
+	(No symbol) [0x0x7ff6ecc3095c]
+	(No symbol) [0x0x7ff6ecc83d07]
+	(No symbol) [0x0x7ff6ecc5890f]
+	(No symbol) [0x0x7ff6ecc80b07]
+	(No symbol) [0x0x7ff6ecc586a3]
+	(No symbol) [0x0x7ff6ecc21791]
+	(No symbol) [0x0x7ff6ecc22523]
+	GetHandleVerifier [0x0x7ff6ed0f684d+3059501]
+	GetHandleVerifier [0x0x7ff6ed0f0c0d+3035885]
+	GetHandleVerifier [0x0x7ff6ed110400+3164896]
+	GetHandleVerifier [0x0x7ff6ece38c3e+185118]
+	GetHandleVerifier [0x0x7ff6ece4054f+216111]
+	GetHandleVerifier [0x0x7ff6ece272e4+113092]
+	GetHandleVerifier [0x0x7ff6ece27499+113529]
+	GetHandleVerifier [0x0x7ff6ece0e298+10616]
 	BaseThreadInitThunk [0x0x7ffb1377e8d7+23]
 	RtlUserThreadStart [0x0x7ffb157fc34c+44]
 </t>
@@ -3471,25 +3471,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=138.0.7204.169); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff7bc3ce935+77845]
-	GetHandleVerifier [0x0x7ff7bc3ce990+77936]
-	(No symbol) [0x0x7ff7bc189cda]
-	(No symbol) [0x0x7ff7bc1e06aa]
-	(No symbol) [0x0x7ff7bc1e095c]
-	(No symbol) [0x0x7ff7bc233d07]
-	(No symbol) [0x0x7ff7bc20890f]
-	(No symbol) [0x0x7ff7bc230b07]
-	(No symbol) [0x0x7ff7bc2086a3]
-	(No symbol) [0x0x7ff7bc1d1791]
-	(No symbol) [0x0x7ff7bc1d2523]
-	GetHandleVerifier [0x0x7ff7bc6a684d+3059501]
-	GetHandleVerifier [0x0x7ff7bc6a0c0d+3035885]
-	GetHandleVerifier [0x0x7ff7bc6c0400+3164896]
-	GetHandleVerifier [0x0x7ff7bc3e8c3e+185118]
-	GetHandleVerifier [0x0x7ff7bc3f054f+216111]
-	GetHandleVerifier [0x0x7ff7bc3d72e4+113092]
-	GetHandleVerifier [0x0x7ff7bc3d7499+113529]
-	GetHandleVerifier [0x0x7ff7bc3be298+10616]
+	GetHandleVerifier [0x0x7ff6ece1e935+77845]
+	GetHandleVerifier [0x0x7ff6ece1e990+77936]
+	(No symbol) [0x0x7ff6ecbd9cda]
+	(No symbol) [0x0x7ff6ecc306aa]
+	(No symbol) [0x0x7ff6ecc3095c]
+	(No symbol) [0x0x7ff6ecc83d07]
+	(No symbol) [0x0x7ff6ecc5890f]
+	(No symbol) [0x0x7ff6ecc80b07]
+	(No symbol) [0x0x7ff6ecc586a3]
+	(No symbol) [0x0x7ff6ecc21791]
+	(No symbol) [0x0x7ff6ecc22523]
+	GetHandleVerifier [0x0x7ff6ed0f684d+3059501]
+	GetHandleVerifier [0x0x7ff6ed0f0c0d+3035885]
+	GetHandleVerifier [0x0x7ff6ed110400+3164896]
+	GetHandleVerifier [0x0x7ff6ece38c3e+185118]
+	GetHandleVerifier [0x0x7ff6ece4054f+216111]
+	GetHandleVerifier [0x0x7ff6ece272e4+113092]
+	GetHandleVerifier [0x0x7ff6ece27499+113529]
+	GetHandleVerifier [0x0x7ff6ece0e298+10616]
 	BaseThreadInitThunk [0x0x7ffb1377e8d7+23]
 	RtlUserThreadStart [0x0x7ffb157fc34c+44]
 </t>
